--- a/snnTorch/New Microsoft Excel Worksheet.xlsx
+++ b/snnTorch/New Microsoft Excel Worksheet.xlsx
@@ -19,10 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="14">
-  <si>
-    <t>C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="13">
   <si>
     <t>adapt20_3b</t>
   </si>
@@ -60,7 +57,7 @@
     <t>dsb4updn_median_200_16b</t>
   </si>
   <si>
-    <t>testing_dsb4</t>
+    <t>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py</t>
   </si>
 </sst>
 </file>
@@ -384,737 +381,593 @@
   <dimension ref="A1:L80"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="11.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.53515625" customWidth="1"/>
     <col min="3" max="3" width="3.84375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
-      <c r="D2" t="s">
-        <v>13</v>
-      </c>
       <c r="L2" t="str">
-        <f>$A$2 &amp; " --prefix " &amp; B2 &amp; " --adapt " &amp; C2 &amp; " --identifier " &amp; D2 &amp; " --test_dsb4 "</f>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix dsb4updn_median_200_15f --adapt 0 --identifier testing_dsb4 --test_dsb4 </v>
+        <f>$A$2 &amp; " --prefix " &amp; B2 &amp; " --adapt " &amp; C2</f>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix dsb4updn_median_200_15f --adapt 0</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
         <v>120</v>
       </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
       <c r="L3" t="str">
-        <f t="shared" ref="L3:L49" si="0">$A$2 &amp; " --prefix " &amp; B3 &amp; " --adapt " &amp; C3 &amp; " --identifier " &amp; D3 &amp; " --test_dsb4 "</f>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix dsb4updn_median_200_15f --adapt 120 --identifier testing_dsb4 --test_dsb4 </v>
+        <f t="shared" ref="L3:L49" si="0">$A$2 &amp; " --prefix " &amp; B3 &amp; " --adapt " &amp; C3</f>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix dsb4updn_median_200_15f --adapt 120</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4">
         <v>20</v>
       </c>
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
       <c r="L4" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix dsb4updn_median_200_15f --adapt 20 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix dsb4updn_median_200_15f --adapt 20</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5">
         <v>2</v>
-      </c>
-      <c r="D5" t="s">
-        <v>13</v>
       </c>
       <c r="F5" s="1"/>
       <c r="L5" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix dsb4updn_median_200_15f --adapt 2 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix dsb4updn_median_200_15f --adapt 2</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B6" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
-      <c r="D6" t="s">
-        <v>13</v>
-      </c>
       <c r="L6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix dsb4updn_median_200_11b --adapt 0 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix dsb4updn_median_200_11b --adapt 0</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7">
         <v>120</v>
       </c>
-      <c r="D7" t="s">
-        <v>13</v>
-      </c>
       <c r="L7" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix dsb4updn_median_200_11b --adapt 120 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix dsb4updn_median_200_11b --adapt 120</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8">
         <v>20</v>
       </c>
-      <c r="D8" t="s">
-        <v>13</v>
-      </c>
       <c r="L8" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix dsb4updn_median_200_11b --adapt 20 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix dsb4updn_median_200_11b --adapt 20</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B9" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9">
         <v>2</v>
       </c>
-      <c r="D9" t="s">
-        <v>13</v>
-      </c>
       <c r="L9" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix dsb4updn_median_200_11b --adapt 2 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix dsb4updn_median_200_11b --adapt 2</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B10" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
-      <c r="D10" t="s">
-        <v>13</v>
-      </c>
       <c r="L10" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix dsb4updn_median_200_13f --adapt 0 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix dsb4updn_median_200_13f --adapt 0</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B11" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11">
         <v>120</v>
       </c>
-      <c r="D11" t="s">
-        <v>13</v>
-      </c>
       <c r="L11" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix dsb4updn_median_200_13f --adapt 120 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix dsb4updn_median_200_13f --adapt 120</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B12" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C12">
         <v>20</v>
       </c>
-      <c r="D12" t="s">
-        <v>13</v>
-      </c>
       <c r="L12" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix dsb4updn_median_200_13f --adapt 20 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix dsb4updn_median_200_13f --adapt 20</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C13">
         <v>2</v>
       </c>
-      <c r="D13" t="s">
-        <v>13</v>
-      </c>
       <c r="L13" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix dsb4updn_median_200_13f --adapt 2 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix dsb4updn_median_200_13f --adapt 2</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B14" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
-      <c r="D14" t="s">
-        <v>13</v>
-      </c>
       <c r="L14" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix dsb4updn_median_200_9f --adapt 0 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix dsb4updn_median_200_9f --adapt 0</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B15" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C15">
         <v>120</v>
       </c>
-      <c r="D15" t="s">
-        <v>13</v>
-      </c>
       <c r="L15" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix dsb4updn_median_200_9f --adapt 120 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix dsb4updn_median_200_9f --adapt 120</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B16" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16">
         <v>20</v>
       </c>
-      <c r="D16" t="s">
-        <v>13</v>
-      </c>
       <c r="L16" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix dsb4updn_median_200_9f --adapt 20 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix dsb4updn_median_200_9f --adapt 20</v>
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B17" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C17">
         <v>2</v>
       </c>
-      <c r="D17" t="s">
-        <v>13</v>
-      </c>
       <c r="L17" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix dsb4updn_median_200_9f --adapt 2 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix dsb4updn_median_200_9f --adapt 2</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
-      <c r="D18" t="s">
-        <v>13</v>
-      </c>
       <c r="L18" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix dsb4updn_median_200_12b --adapt 0 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix dsb4updn_median_200_12b --adapt 0</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C19">
         <v>120</v>
       </c>
-      <c r="D19" t="s">
-        <v>13</v>
-      </c>
       <c r="L19" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix dsb4updn_median_200_12b --adapt 120 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix dsb4updn_median_200_12b --adapt 120</v>
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B20" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C20">
         <v>20</v>
       </c>
-      <c r="D20" t="s">
-        <v>13</v>
-      </c>
       <c r="L20" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix dsb4updn_median_200_12b --adapt 20 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix dsb4updn_median_200_12b --adapt 20</v>
       </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C21">
         <v>2</v>
       </c>
-      <c r="D21" t="s">
-        <v>13</v>
-      </c>
       <c r="L21" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix dsb4updn_median_200_12b --adapt 2 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix dsb4updn_median_200_12b --adapt 2</v>
       </c>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B22" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
-      <c r="D22" t="s">
-        <v>13</v>
-      </c>
       <c r="L22" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix updnb4ds_100_13b --adapt 0 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix updnb4ds_100_13b --adapt 0</v>
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B23" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C23">
         <v>120</v>
       </c>
-      <c r="D23" t="s">
-        <v>13</v>
-      </c>
       <c r="L23" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix updnb4ds_100_13b --adapt 120 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix updnb4ds_100_13b --adapt 120</v>
       </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B24" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C24">
         <v>20</v>
       </c>
-      <c r="D24" t="s">
-        <v>13</v>
-      </c>
       <c r="L24" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix updnb4ds_100_13b --adapt 20 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix updnb4ds_100_13b --adapt 20</v>
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B25" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C25">
         <v>2</v>
       </c>
-      <c r="D25" t="s">
-        <v>13</v>
-      </c>
       <c r="L25" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix updnb4ds_100_13b --adapt 2 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix updnb4ds_100_13b --adapt 2</v>
       </c>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B26" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C26">
         <v>0</v>
       </c>
-      <c r="D26" t="s">
-        <v>13</v>
-      </c>
       <c r="L26" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix updnb4ds_100_7 --adapt 0 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix updnb4ds_100_7 --adapt 0</v>
       </c>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B27" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C27">
         <v>120</v>
       </c>
-      <c r="D27" t="s">
-        <v>13</v>
-      </c>
       <c r="L27" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix updnb4ds_100_7 --adapt 120 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix updnb4ds_100_7 --adapt 120</v>
       </c>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B28" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C28">
         <v>20</v>
       </c>
-      <c r="D28" t="s">
-        <v>13</v>
-      </c>
       <c r="L28" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix updnb4ds_100_7 --adapt 20 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix updnb4ds_100_7 --adapt 20</v>
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B29" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C29">
         <v>2</v>
       </c>
-      <c r="D29" t="s">
-        <v>13</v>
-      </c>
       <c r="L29" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix updnb4ds_100_7 --adapt 2 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix updnb4ds_100_7 --adapt 2</v>
       </c>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C30">
         <v>0</v>
       </c>
-      <c r="D30" t="s">
-        <v>13</v>
-      </c>
       <c r="L30" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix updnb4ds_100_13f --adapt 0 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix updnb4ds_100_13f --adapt 0</v>
       </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B31" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C31">
         <v>120</v>
       </c>
-      <c r="D31" t="s">
-        <v>13</v>
-      </c>
       <c r="L31" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix updnb4ds_100_13f --adapt 120 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix updnb4ds_100_13f --adapt 120</v>
       </c>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B32" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C32">
         <v>20</v>
       </c>
-      <c r="D32" t="s">
-        <v>13</v>
-      </c>
       <c r="L32" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix updnb4ds_100_13f --adapt 20 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix updnb4ds_100_13f --adapt 20</v>
       </c>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B33" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C33">
         <v>2</v>
       </c>
-      <c r="D33" t="s">
-        <v>13</v>
-      </c>
       <c r="L33" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix updnb4ds_100_13f --adapt 2 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix updnb4ds_100_13f --adapt 2</v>
       </c>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B34" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C34">
         <v>0</v>
       </c>
-      <c r="D34" t="s">
-        <v>13</v>
-      </c>
       <c r="L34" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix adapt20_3b --adapt 0 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix adapt20_3b --adapt 0</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B35" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C35">
         <v>120</v>
       </c>
-      <c r="D35" t="s">
-        <v>13</v>
-      </c>
       <c r="L35" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix adapt20_3b --adapt 120 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix adapt20_3b --adapt 120</v>
       </c>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B36" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C36">
         <v>20</v>
       </c>
-      <c r="D36" t="s">
-        <v>13</v>
-      </c>
       <c r="L36" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix adapt20_3b --adapt 20 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix adapt20_3b --adapt 20</v>
       </c>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B37" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C37">
         <v>2</v>
       </c>
-      <c r="D37" t="s">
-        <v>13</v>
-      </c>
       <c r="L37" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix adapt20_3b --adapt 2 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix adapt20_3b --adapt 2</v>
       </c>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B38" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C38">
         <v>0</v>
       </c>
-      <c r="D38" t="s">
-        <v>13</v>
-      </c>
       <c r="L38" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix dsb4updn_median_200_11f --adapt 0 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix dsb4updn_median_200_11f --adapt 0</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B39" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C39">
         <v>120</v>
       </c>
-      <c r="D39" t="s">
-        <v>13</v>
-      </c>
       <c r="L39" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix dsb4updn_median_200_11f --adapt 120 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix dsb4updn_median_200_11f --adapt 120</v>
       </c>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B40" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C40">
         <v>20</v>
       </c>
-      <c r="D40" t="s">
-        <v>13</v>
-      </c>
       <c r="L40" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix dsb4updn_median_200_11f --adapt 20 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix dsb4updn_median_200_11f --adapt 20</v>
       </c>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B41" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C41">
         <v>2</v>
       </c>
-      <c r="D41" t="s">
-        <v>13</v>
-      </c>
       <c r="L41" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix dsb4updn_median_200_11f --adapt 2 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix dsb4updn_median_200_11f --adapt 2</v>
       </c>
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B42" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C42">
         <v>0</v>
       </c>
-      <c r="D42" t="s">
-        <v>13</v>
-      </c>
       <c r="L42" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix dsb4updn_median_200_14b --adapt 0 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix dsb4updn_median_200_14b --adapt 0</v>
       </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B43" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C43">
         <v>120</v>
       </c>
-      <c r="D43" t="s">
-        <v>13</v>
-      </c>
       <c r="L43" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix dsb4updn_median_200_14b --adapt 120 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix dsb4updn_median_200_14b --adapt 120</v>
       </c>
     </row>
     <row r="44" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B44" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C44">
         <v>20</v>
       </c>
-      <c r="D44" t="s">
-        <v>13</v>
-      </c>
       <c r="L44" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix dsb4updn_median_200_14b --adapt 20 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix dsb4updn_median_200_14b --adapt 20</v>
       </c>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B45" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C45">
         <v>2</v>
       </c>
-      <c r="D45" t="s">
-        <v>13</v>
-      </c>
       <c r="L45" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix dsb4updn_median_200_14b --adapt 2 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix dsb4updn_median_200_14b --adapt 2</v>
       </c>
     </row>
     <row r="46" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B46" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C46">
         <v>0</v>
       </c>
-      <c r="D46" t="s">
-        <v>13</v>
-      </c>
       <c r="L46" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix dsb4updn_median_200_16b --adapt 0 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix dsb4updn_median_200_16b --adapt 0</v>
       </c>
     </row>
     <row r="47" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B47" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C47">
         <v>120</v>
       </c>
-      <c r="D47" t="s">
-        <v>13</v>
-      </c>
       <c r="L47" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix dsb4updn_median_200_16b --adapt 120 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix dsb4updn_median_200_16b --adapt 120</v>
       </c>
     </row>
     <row r="48" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C48">
         <v>20</v>
       </c>
-      <c r="D48" t="s">
-        <v>13</v>
-      </c>
       <c r="L48" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix dsb4updn_median_200_16b --adapt 20 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix dsb4updn_median_200_16b --adapt 20</v>
       </c>
     </row>
     <row r="49" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B49" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C49">
         <v>2</v>
       </c>
-      <c r="D49" t="s">
-        <v>13</v>
-      </c>
       <c r="L49" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">C:/Users/NCN/Miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/batchrun.py --prefix dsb4updn_median_200_16b --adapt 2 --identifier testing_dsb4 --test_dsb4 </v>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py --prefix dsb4updn_median_200_16b --adapt 2</v>
       </c>
     </row>
     <row r="80" spans="5:5" x14ac:dyDescent="0.4">

--- a/snnTorch/New Microsoft Excel Worksheet.xlsx
+++ b/snnTorch/New Microsoft Excel Worksheet.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12643"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12643" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1 (2)" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="14">
   <si>
     <t>adapt20_3b</t>
   </si>
@@ -58,6 +59,9 @@
   </si>
   <si>
     <t>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/generalization_madrid/batchrun.py</t>
+  </si>
+  <si>
+    <t>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py</t>
   </si>
 </sst>
 </file>
@@ -977,4 +981,607 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L80"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="2" max="2" width="35.53515625" customWidth="1"/>
+    <col min="3" max="3" width="3.84375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="L2" t="str">
+        <f>$A$2 &amp; " --prefix " &amp; B2 &amp; " --adapt " &amp; C2</f>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix dsb4updn_median_200_15f --adapt 0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>120</v>
+      </c>
+      <c r="L3" t="str">
+        <f t="shared" ref="L3:L49" si="0">$A$2 &amp; " --prefix " &amp; B3 &amp; " --adapt " &amp; C3</f>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix dsb4updn_median_200_15f --adapt 120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>20</v>
+      </c>
+      <c r="L4" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix dsb4updn_median_200_15f --adapt 20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="L5" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix dsb4updn_median_200_15f --adapt 2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="L6" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix dsb4updn_median_200_11b --adapt 0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>120</v>
+      </c>
+      <c r="L7" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix dsb4updn_median_200_11b --adapt 120</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <v>20</v>
+      </c>
+      <c r="L8" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix dsb4updn_median_200_11b --adapt 20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="L9" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix dsb4updn_median_200_11b --adapt 2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="L10" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix dsb4updn_median_200_13f --adapt 0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11">
+        <v>120</v>
+      </c>
+      <c r="L11" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix dsb4updn_median_200_13f --adapt 120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12">
+        <v>20</v>
+      </c>
+      <c r="L12" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix dsb4updn_median_200_13f --adapt 20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="L13" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix dsb4updn_median_200_13f --adapt 2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="L14" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix dsb4updn_median_200_9f --adapt 0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B15" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15">
+        <v>120</v>
+      </c>
+      <c r="L15" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix dsb4updn_median_200_9f --adapt 120</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16">
+        <v>20</v>
+      </c>
+      <c r="L16" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix dsb4updn_median_200_9f --adapt 20</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="L17" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix dsb4updn_median_200_9f --adapt 2</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="L18" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix dsb4updn_median_200_12b --adapt 0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19">
+        <v>120</v>
+      </c>
+      <c r="L19" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix dsb4updn_median_200_12b --adapt 120</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B20" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20">
+        <v>20</v>
+      </c>
+      <c r="L20" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix dsb4updn_median_200_12b --adapt 20</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="L21" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix dsb4updn_median_200_12b --adapt 2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="L22" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix updnb4ds_100_13b --adapt 0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B23" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23">
+        <v>120</v>
+      </c>
+      <c r="L23" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix updnb4ds_100_13b --adapt 120</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B24" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24">
+        <v>20</v>
+      </c>
+      <c r="L24" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix updnb4ds_100_13b --adapt 20</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="L25" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix updnb4ds_100_13b --adapt 2</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="L26" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix updnb4ds_100_7 --adapt 0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B27" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27">
+        <v>120</v>
+      </c>
+      <c r="L27" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix updnb4ds_100_7 --adapt 120</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B28" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28">
+        <v>20</v>
+      </c>
+      <c r="L28" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix updnb4ds_100_7 --adapt 20</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B29" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+      <c r="L29" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix updnb4ds_100_7 --adapt 2</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B30" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="L30" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix updnb4ds_100_13f --adapt 0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B31" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31">
+        <v>120</v>
+      </c>
+      <c r="L31" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix updnb4ds_100_13f --adapt 120</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B32" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32">
+        <v>20</v>
+      </c>
+      <c r="L32" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix updnb4ds_100_13f --adapt 20</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B33" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33">
+        <v>2</v>
+      </c>
+      <c r="L33" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix updnb4ds_100_13f --adapt 2</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B34" t="s">
+        <v>0</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="L34" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix adapt20_3b --adapt 0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B35" t="s">
+        <v>0</v>
+      </c>
+      <c r="C35">
+        <v>120</v>
+      </c>
+      <c r="L35" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix adapt20_3b --adapt 120</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B36" t="s">
+        <v>0</v>
+      </c>
+      <c r="C36">
+        <v>20</v>
+      </c>
+      <c r="L36" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix adapt20_3b --adapt 20</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B37" t="s">
+        <v>0</v>
+      </c>
+      <c r="C37">
+        <v>2</v>
+      </c>
+      <c r="L37" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix adapt20_3b --adapt 2</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B38" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="L38" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix dsb4updn_median_200_11f --adapt 0</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39">
+        <v>120</v>
+      </c>
+      <c r="L39" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix dsb4updn_median_200_11f --adapt 120</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B40" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40">
+        <v>20</v>
+      </c>
+      <c r="L40" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix dsb4updn_median_200_11f --adapt 20</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B41" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41">
+        <v>2</v>
+      </c>
+      <c r="L41" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix dsb4updn_median_200_11f --adapt 2</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B42" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+      <c r="L42" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix dsb4updn_median_200_14b --adapt 0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B43" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43">
+        <v>120</v>
+      </c>
+      <c r="L43" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix dsb4updn_median_200_14b --adapt 120</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B44" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44">
+        <v>20</v>
+      </c>
+      <c r="L44" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix dsb4updn_median_200_14b --adapt 20</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B45" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45">
+        <v>2</v>
+      </c>
+      <c r="L45" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix dsb4updn_median_200_14b --adapt 2</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B46" t="s">
+        <v>11</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+      <c r="L46" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix dsb4updn_median_200_16b --adapt 0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B47" t="s">
+        <v>11</v>
+      </c>
+      <c r="C47">
+        <v>120</v>
+      </c>
+      <c r="L47" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix dsb4updn_median_200_16b --adapt 120</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B48" t="s">
+        <v>11</v>
+      </c>
+      <c r="C48">
+        <v>20</v>
+      </c>
+      <c r="L48" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix dsb4updn_median_200_16b --adapt 20</v>
+      </c>
+    </row>
+    <row r="49" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B49" t="s">
+        <v>11</v>
+      </c>
+      <c r="C49">
+        <v>2</v>
+      </c>
+      <c r="L49" t="str">
+        <f t="shared" si="0"/>
+        <v>C:/Users/NCN/miniconda3/envs/lava_snn_ripples/python.exe c:/Users/NCN/Documents/PedroFelix/LAVA_SNN_ripples/snnTorch/retry_live_val/batchrun.py --prefix dsb4updn_median_200_16b --adapt 2</v>
+      </c>
+    </row>
+    <row r="80" spans="5:5" x14ac:dyDescent="0.4">
+      <c r="E80" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>